--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008F7A4B-86B6-4F9C-8BD1-AD4E6EE749B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCADC871-E717-4DED-8A42-FC90AC248F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="1380" windowWidth="28800" windowHeight="15345" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="39285" yWindow="1500" windowWidth="33285" windowHeight="16605" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1219,18 +1219,18 @@
         <f>G13-B2</f>
         <v>2201.9003994796713</v>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="20">
         <v>32</v>
       </c>
-      <c r="K13" s="30">
+      <c r="K13" s="21">
         <f>K12*(1+C2)</f>
         <v>13749.406785310975</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="21">
         <f>K12*C2</f>
         <v>136.13274044862351</v>
       </c>
-      <c r="M13" s="31">
+      <c r="M13" s="22">
         <f>K13-B2</f>
         <v>3749.4067853109755</v>
       </c>

--- a/Amoritization.xlsx
+++ b/Amoritization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCADC871-E717-4DED-8A42-FC90AC248F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48729A9-B649-4EAC-98AC-3B2E52F664A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39285" yWindow="1500" windowWidth="33285" windowHeight="16605" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
+    <workbookView xWindow="38745" yWindow="360" windowWidth="30435" windowHeight="16605" xr2:uid="{AE14A5DA-5418-4CB2-B16F-47804216F2DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -663,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83046D5A-2E5B-4B8F-925A-51AAA62DB907}">
-  <dimension ref="A2:U34"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -687,16 +687,21 @@
     <col min="21" max="21" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="10">
+        <v>4.3900000000000002E-2</v>
+      </c>
+    </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
-        <v>4.3900000000000002E-2</v>
+        <v>0.08</v>
       </c>
       <c r="B2" s="1">
         <v>10000</v>
       </c>
       <c r="C2" s="11">
-        <f>A4/12</f>
-        <v>0.01</v>
+        <f>A2/12</f>
+        <v>6.6666666666666671E-3</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -778,67 +783,67 @@
       </c>
       <c r="C6" s="21">
         <f>B2*(1+C2)</f>
-        <v>10100</v>
+        <v>10066.666666666666</v>
       </c>
       <c r="D6" s="21">
         <f>B2*C2</f>
-        <v>100</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="E6" s="22">
         <f>C6-B2</f>
-        <v>100</v>
+        <v>66.66666666666606</v>
       </c>
       <c r="F6" s="20">
         <v>13</v>
       </c>
       <c r="G6" s="21">
         <f>C17*(1+C2)</f>
-        <v>11380.932804332895</v>
+        <v>10902.195035195598</v>
       </c>
       <c r="H6" s="21">
         <f>C17*C2</f>
-        <v>112.68250301319699</v>
+        <v>72.199967120500659</v>
       </c>
       <c r="I6" s="22">
         <f>G6-B2</f>
-        <v>1380.9328043328951</v>
+        <v>902.19503519559839</v>
       </c>
       <c r="J6" s="20">
         <v>25</v>
       </c>
       <c r="K6" s="21">
         <f>G17*(1+C2)</f>
-        <v>12824.319950172341</v>
+        <v>11807.071846236118</v>
       </c>
       <c r="L6" s="21">
         <f>G17*C2</f>
-        <v>126.97346485319149</v>
+        <v>78.192528783020663</v>
       </c>
       <c r="M6" s="22">
         <f>K6-B2</f>
-        <v>2824.3199501723411</v>
+        <v>1807.0718462361183</v>
       </c>
       <c r="N6" s="32">
         <v>37</v>
       </c>
       <c r="O6" s="33">
         <f>K17*(1+C2)</f>
-        <v>14450.764714274967</v>
+        <v>12787.052986314553</v>
       </c>
       <c r="P6" s="33">
         <f>K17*C2</f>
-        <v>143.07687835915809</v>
+        <v>84.682470108043404</v>
       </c>
       <c r="Q6" s="34">
         <f>O6-B2</f>
-        <v>4450.7647142749665</v>
+        <v>2787.052986314553</v>
       </c>
       <c r="S6" s="35" t="s">
         <v>1</v>
       </c>
       <c r="T6" s="36">
         <f>O6-B2</f>
-        <v>4450.7647142749665</v>
+        <v>2787.052986314553</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -850,45 +855,45 @@
       </c>
       <c r="C7" s="25">
         <f>C6*(1+C2)</f>
-        <v>10201</v>
+        <v>10133.777777777777</v>
       </c>
       <c r="D7" s="25">
         <f>C6*C2</f>
-        <v>101</v>
+        <v>67.111111111111114</v>
       </c>
       <c r="E7" s="26">
         <f>C7-B2</f>
-        <v>201</v>
+        <v>133.77777777777737</v>
       </c>
       <c r="F7" s="24">
         <v>14</v>
       </c>
       <c r="G7" s="25">
         <f>G6*(1+C2)</f>
-        <v>11494.742132376225</v>
+        <v>10974.876335430235</v>
       </c>
       <c r="H7" s="25">
         <f>G6*C2</f>
-        <v>113.80932804332895</v>
+        <v>72.681300234637334</v>
       </c>
       <c r="I7" s="26">
         <f>G7-B2</f>
-        <v>1494.7421323762246</v>
+        <v>974.87633543023549</v>
       </c>
       <c r="J7" s="24">
         <v>26</v>
       </c>
       <c r="K7" s="25">
         <f>K6*(1+C2)</f>
-        <v>12952.563149674064</v>
+        <v>11885.785658544359</v>
       </c>
       <c r="L7" s="25">
         <f>K6*C2</f>
-        <v>128.24319950172341</v>
+        <v>78.71381230824079</v>
       </c>
       <c r="M7" s="26">
         <f>K7-B2</f>
-        <v>2952.5631496740643</v>
+        <v>1885.7856585443587</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -899,7 +904,7 @@
       </c>
       <c r="T7" s="28">
         <f>B2+T6</f>
-        <v>14450.764714274967</v>
+        <v>12787.052986314553</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -911,45 +916,45 @@
       </c>
       <c r="C8" s="21">
         <f>C7*(1+C2)</f>
-        <v>10303.01</v>
+        <v>10201.336296296295</v>
       </c>
       <c r="D8" s="21">
         <f>C7*C2</f>
-        <v>102.01</v>
+        <v>67.558518518518525</v>
       </c>
       <c r="E8" s="22">
         <f>C8-B2</f>
-        <v>303.01000000000022</v>
+        <v>201.33629629629468</v>
       </c>
       <c r="F8" s="20">
         <v>15</v>
       </c>
       <c r="G8" s="21">
         <f>G7*(1+C2)</f>
-        <v>11609.689553699987</v>
+        <v>11048.042177666437</v>
       </c>
       <c r="H8" s="21">
         <f>G7*C2</f>
-        <v>114.94742132376224</v>
+        <v>73.16584223620157</v>
       </c>
       <c r="I8" s="22">
         <f>G8-B2</f>
-        <v>1609.6895536999873</v>
+        <v>1048.0421776664371</v>
       </c>
       <c r="J8" s="20">
         <v>27</v>
       </c>
       <c r="K8" s="21">
         <f>K7*(1+C2)</f>
-        <v>13082.088781170805</v>
+        <v>11965.02422960132</v>
       </c>
       <c r="L8" s="21">
         <f>K7*C2</f>
-        <v>129.52563149674066</v>
+        <v>79.2385710569624</v>
       </c>
       <c r="M8" s="22">
         <f>K8-B2</f>
-        <v>3082.0887811708053</v>
+        <v>1965.0242296013203</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -960,7 +965,7 @@
       </c>
       <c r="T8" s="27">
         <f>T7-B2</f>
-        <v>4450.7647142749665</v>
+        <v>2787.052986314553</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -972,45 +977,45 @@
       </c>
       <c r="C9" s="25">
         <f>C8*(1+C2)</f>
-        <v>10406.0401</v>
+        <v>10269.345204938269</v>
       </c>
       <c r="D9" s="25">
         <f>C8*C2</f>
-        <v>103.0301</v>
+        <v>68.008908641975296</v>
       </c>
       <c r="E9" s="26">
         <f>C9-B2</f>
-        <v>406.04010000000017</v>
+        <v>269.34520493826858</v>
       </c>
       <c r="F9" s="24">
         <v>16</v>
       </c>
       <c r="G9" s="25">
         <f>G8*(1+C2)</f>
-        <v>11725.786449236988</v>
+        <v>11121.695792184213</v>
       </c>
       <c r="H9" s="25">
         <f>G8*C2</f>
-        <v>116.09689553699988</v>
+        <v>73.653614517776248</v>
       </c>
       <c r="I9" s="26">
         <f>G9-B2</f>
-        <v>1725.7864492369881</v>
+        <v>1121.6957921842131</v>
       </c>
       <c r="J9" s="24">
         <v>28</v>
       </c>
       <c r="K9" s="25">
         <f>K8*(1+C2)</f>
-        <v>13212.909668982513</v>
+        <v>12044.791057798662</v>
       </c>
       <c r="L9" s="25">
         <f>K8*C2</f>
-        <v>130.82088781170805</v>
+        <v>79.766828197342136</v>
       </c>
       <c r="M9" s="26">
         <f>K9-B2</f>
-        <v>3212.9096689825128</v>
+        <v>2044.7910577986622</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1021,7 +1026,7 @@
       </c>
       <c r="T9" s="39">
         <f>B2-T8</f>
-        <v>5549.2352857250335</v>
+        <v>7212.947013685447</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -1033,45 +1038,45 @@
       </c>
       <c r="C10" s="21">
         <f>C9*(1+C2)</f>
-        <v>10510.100501000001</v>
+        <v>10337.807506304523</v>
       </c>
       <c r="D10" s="21">
         <f>C9*C2</f>
-        <v>104.060401</v>
+        <v>68.462301366255133</v>
       </c>
       <c r="E10" s="22">
         <f>C10-B2</f>
-        <v>510.1005010000008</v>
+        <v>337.80750630452349</v>
       </c>
       <c r="F10" s="20">
         <v>17</v>
       </c>
       <c r="G10" s="21">
         <f>G9*(1+C2)</f>
-        <v>11843.044313729359</v>
+        <v>11195.840430798773</v>
       </c>
       <c r="H10" s="21">
         <f>G9*C2</f>
-        <v>117.25786449236989</v>
+        <v>74.14463861456143</v>
       </c>
       <c r="I10" s="22">
         <f>G10-B2</f>
-        <v>1843.0443137293587</v>
+        <v>1195.840430798773</v>
       </c>
       <c r="J10" s="20">
         <v>19</v>
       </c>
       <c r="K10" s="21">
         <f>K9*(1+C2)</f>
-        <v>13345.038765672338</v>
+        <v>12125.089664850653</v>
       </c>
       <c r="L10" s="21">
         <f>K9*C2</f>
-        <v>132.12909668982513</v>
+        <v>80.298607051991084</v>
       </c>
       <c r="M10" s="22">
         <f>K10-B2</f>
-        <v>3345.0387656723378</v>
+        <v>2125.0896648506532</v>
       </c>
       <c r="N10" s="1"/>
       <c r="P10" s="1"/>
@@ -1086,45 +1091,45 @@
       </c>
       <c r="C11" s="25">
         <f>C10*(1+C2)</f>
-        <v>10615.20150601</v>
+        <v>10406.72622301322</v>
       </c>
       <c r="D11" s="25">
         <f>C10*C2</f>
-        <v>105.10100501000001</v>
+        <v>68.918716708696834</v>
       </c>
       <c r="E11" s="26">
         <f>C11-B2</f>
-        <v>615.20150601000023</v>
+        <v>406.72622301322008</v>
       </c>
       <c r="F11" s="24">
         <v>18</v>
       </c>
       <c r="G11" s="25">
         <f>G10*(1+C2)</f>
-        <v>11961.474756866652</v>
+        <v>11270.479367004098</v>
       </c>
       <c r="H11" s="25">
         <f>G10*C2</f>
-        <v>118.43044313729359</v>
+        <v>74.638936205325152</v>
       </c>
       <c r="I11" s="26">
         <f>G11-B2</f>
-        <v>1961.4747568666517</v>
+        <v>1270.4793670040981</v>
       </c>
       <c r="J11" s="24">
         <v>30</v>
       </c>
       <c r="K11" s="25">
         <f>K10*(1+C2)</f>
-        <v>13478.489153329061</v>
+        <v>12205.923595949656</v>
       </c>
       <c r="L11" s="25">
         <f>K10*C2</f>
-        <v>133.45038765672339</v>
+        <v>80.83393109900436</v>
       </c>
       <c r="M11" s="26">
         <f>K11-B2</f>
-        <v>3478.4891533290611</v>
+        <v>2205.9235959496564</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1140,45 +1145,45 @@
       </c>
       <c r="C12" s="21">
         <f>C11*(1+C2)</f>
-        <v>10721.353521070101</v>
+        <v>10476.104397833307</v>
       </c>
       <c r="D12" s="21">
         <f>C11*C2</f>
-        <v>106.1520150601</v>
+        <v>69.378174820088134</v>
       </c>
       <c r="E12" s="22">
         <f>C12-B2</f>
-        <v>721.35352107010112</v>
+        <v>476.1043978333073</v>
       </c>
       <c r="F12" s="20">
         <v>19</v>
       </c>
       <c r="G12" s="21">
         <f>G11*(1+C2)</f>
-        <v>12081.089504435318</v>
+        <v>11345.615896117459</v>
       </c>
       <c r="H12" s="21">
         <f>G11*C2</f>
-        <v>119.61474756866652</v>
+        <v>75.136529113360652</v>
       </c>
       <c r="I12" s="22">
         <f>G12-B2</f>
-        <v>2081.0895044353183</v>
+        <v>1345.6158961174588</v>
       </c>
       <c r="J12" s="20">
         <v>31</v>
       </c>
       <c r="K12" s="21">
         <f>K11*(1+C2)</f>
-        <v>13613.274044862352</v>
+        <v>12287.296419922654</v>
       </c>
       <c r="L12" s="21">
         <f>K11*C2</f>
-        <v>134.78489153329062</v>
+        <v>81.372823972997708</v>
       </c>
       <c r="M12" s="22">
         <f>K12-B2</f>
-        <v>3613.2740448623517</v>
+        <v>2287.2964199226535</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1194,45 +1199,45 @@
       </c>
       <c r="C13" s="25">
         <f>C12*(1+C2)</f>
-        <v>10828.567056280803</v>
+        <v>10545.945093818862</v>
       </c>
       <c r="D13" s="25">
         <f>C12*C2</f>
-        <v>107.21353521070101</v>
+        <v>69.840695985555385</v>
       </c>
       <c r="E13" s="26">
         <f>C13-B2</f>
-        <v>828.56705628080272</v>
+        <v>545.94509381886201</v>
       </c>
       <c r="F13" s="24">
         <v>20</v>
       </c>
       <c r="G13" s="25">
         <f>G12*(1+C2)</f>
-        <v>12201.900399479671</v>
+        <v>11421.253335424908</v>
       </c>
       <c r="H13" s="25">
         <f>G12*C2</f>
-        <v>120.81089504435319</v>
+        <v>75.637439307449725</v>
       </c>
       <c r="I13" s="26">
         <f>G13-B2</f>
-        <v>2201.9003994796713</v>
+        <v>1421.2533354249081</v>
       </c>
       <c r="J13" s="20">
         <v>32</v>
       </c>
       <c r="K13" s="21">
         <f>K12*(1+C2)</f>
-        <v>13749.406785310975</v>
+        <v>12369.211729388804</v>
       </c>
       <c r="L13" s="21">
         <f>K12*C2</f>
-        <v>136.13274044862351</v>
+        <v>81.915309466151029</v>
       </c>
       <c r="M13" s="22">
         <f>K13-B2</f>
-        <v>3749.4067853109755</v>
+        <v>2369.2117293888041</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1249,45 +1254,45 @@
       </c>
       <c r="C14" s="21">
         <f>C13*(1+C2)</f>
-        <v>10936.85272684361</v>
+        <v>10616.25139444432</v>
       </c>
       <c r="D14" s="21">
         <f>C13*C2</f>
-        <v>108.28567056280804</v>
+        <v>70.306300625459087</v>
       </c>
       <c r="E14" s="22">
         <f>C14-B2</f>
-        <v>936.85272684361007</v>
+        <v>616.25139444431989</v>
       </c>
       <c r="F14" s="20">
         <v>21</v>
       </c>
       <c r="G14" s="21">
         <f>G13*(1+C2)</f>
-        <v>12323.919403474469</v>
+        <v>11497.39502432774</v>
       </c>
       <c r="H14" s="21">
         <f>G13*C2</f>
-        <v>122.01900399479672</v>
+        <v>76.141688902832726</v>
       </c>
       <c r="I14" s="22">
         <f>G14-B2</f>
-        <v>2323.9194034744687</v>
+        <v>1497.3950243277395</v>
       </c>
       <c r="J14" s="32">
         <v>33</v>
       </c>
       <c r="K14" s="33">
         <f>K13*(1+C2)</f>
-        <v>13886.900853164085</v>
+        <v>12451.673140918061</v>
       </c>
       <c r="L14" s="33">
         <f>K13*C2</f>
-        <v>137.49406785310975</v>
+        <v>82.461411529258697</v>
       </c>
       <c r="M14" s="34">
         <f>K14-B2</f>
-        <v>3886.9008531640848</v>
+        <v>2451.6731409180611</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1304,45 +1309,45 @@
       </c>
       <c r="C15" s="25">
         <f>C14*(1+C2)</f>
-        <v>11046.221254112046</v>
+        <v>10687.026403740614</v>
       </c>
       <c r="D15" s="25">
         <f>C14*C2</f>
-        <v>109.3685272684361</v>
+        <v>70.775009296295465</v>
       </c>
       <c r="E15" s="26">
         <f>C15-B2</f>
-        <v>1046.2212541120462</v>
+        <v>687.02640374061411</v>
       </c>
       <c r="F15" s="24">
         <v>22</v>
       </c>
       <c r="G15" s="25">
         <f>G14*(1+C2)</f>
-        <v>12447.158597509213</v>
+        <v>11574.044324489923</v>
       </c>
       <c r="H15" s="25">
         <f>G14*C2</f>
-        <v>123.23919403474468</v>
+        <v>76.649300162184929</v>
       </c>
       <c r="I15" s="26">
         <f>G15-B2</f>
-        <v>2447.158597509213</v>
+        <v>1574.0443244899234</v>
       </c>
       <c r="J15" s="29">
         <v>34</v>
       </c>
       <c r="K15" s="30">
         <f>K14*(1+C2)</f>
-        <v>14025.769861695726</v>
+        <v>12534.684295190847</v>
       </c>
       <c r="L15" s="30">
         <f>K14*C2</f>
-        <v>138.86900853164084</v>
+        <v>83.011154272787081</v>
       </c>
       <c r="M15" s="31">
         <f>K15-B2</f>
-        <v>4025.7698616957259</v>
+        <v>2534.6842951908475</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1358,45 +1363,45 @@
       </c>
       <c r="C16" s="21">
         <f>C15*(1+C2)</f>
-        <v>11156.683466653167</v>
+        <v>10758.273246432218</v>
       </c>
       <c r="D16" s="21">
         <f>C15*C2</f>
-        <v>110.46221254112046</v>
+        <v>71.246842691604101</v>
       </c>
       <c r="E16" s="22">
         <f>C16-B2</f>
-        <v>1156.6834666531668</v>
+        <v>758.273246432218</v>
       </c>
       <c r="F16" s="20">
         <v>23</v>
       </c>
       <c r="G16" s="21">
         <f>G15*(1+C2)</f>
-        <v>12571.630183484305</v>
+        <v>11651.204619986522</v>
       </c>
       <c r="H16" s="21">
         <f>G15*C2</f>
-        <v>124.47158597509214</v>
+        <v>77.160295496599488</v>
       </c>
       <c r="I16" s="22">
         <f>G16-B2</f>
-        <v>2571.6301834843052</v>
+        <v>1651.2046199865217</v>
       </c>
       <c r="J16" s="32">
         <v>35</v>
       </c>
       <c r="K16" s="33">
         <f>K15*(1+C2)</f>
-        <v>14166.027560312683</v>
+        <v>12618.248857158786</v>
       </c>
       <c r="L16" s="33">
         <f>K15*C2</f>
-        <v>140.25769861695727</v>
+        <v>83.564561967938985</v>
       </c>
       <c r="M16" s="34">
         <f>K16-B2</f>
-        <v>4166.0275603126829</v>
+        <v>2618.2488571587855</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -1412,45 +1417,45 @@
       </c>
       <c r="C17" s="25">
         <f>C16*(1+C2)</f>
-        <v>11268.250301319698</v>
+        <v>10829.995068075099</v>
       </c>
       <c r="D17" s="25">
         <f>C16*C2</f>
-        <v>111.56683466653168</v>
+        <v>71.721821642881451</v>
       </c>
       <c r="E17" s="26">
         <f>C17-B2</f>
-        <v>1268.2503013196983</v>
+        <v>829.99506807509897</v>
       </c>
       <c r="F17" s="24">
         <v>24</v>
       </c>
       <c r="G17" s="25">
         <f>G16*(1+C2)</f>
-        <v>12697.346485319149</v>
+        <v>11728.879317453098</v>
       </c>
       <c r="H17" s="25">
         <f>G16*C2</f>
-        <v>125.71630183484305</v>
+        <v>77.674697466576816</v>
       </c>
       <c r="I17" s="26">
         <f>G17-B2</f>
-        <v>2697.346485319149</v>
+        <v>1728.8793174530983</v>
       </c>
       <c r="J17" s="29">
         <v>36</v>
       </c>
       <c r="K17" s="30">
         <f>K16*(1+C2)</f>
-        <v>14307.687835915809</v>
+        <v>12702.370516206511</v>
       </c>
       <c r="L17" s="30">
         <f>K16*C2</f>
-        <v>141.66027560312682</v>
+        <v>84.121659047725245</v>
       </c>
       <c r="M17" s="31">
         <f>K17-B2</f>
-        <v>4307.687835915809</v>
+        <v>2702.3705162065107</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -1503,7 +1508,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
-        <f>A2</f>
+        <f>A1</f>
         <v>4.3900000000000002E-2</v>
       </c>
       <c r="B20" s="1">
